--- a/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week08_19Oct.xlsx
+++ b/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week08_19Oct.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Reviewed by</t>
   </si>
   <si>
-    <t xml:space="preserve">SMSC/BV this week: Black History Month culminates (half-term Fri 23 Oct) — fold the celebration into Build's community action and the Festivals-of-Light showcase.  EVIDENCE: showcase + impact-wall photos + EFL: cultural; complete this half-term's rows in the SMSC Evidence Tracker.</t>
+    <t xml:space="preserve">SMSC/BV this week: Black History Month culminates (half-term Fri 23 Oct) — fold the celebration into Build's community action and the Festivals-of-Light showcase.  EVIDENCE: showcase + impact-wall photos + evidence platform: cultural; complete this half-term's rows in the SMSC Evidence Tracker.</t>
   </si>
   <si>
     <t xml:space="preserve">Subject</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  Ordering real packets is the assessment — the check is a record of it, not the event itself. Told the format a week ahead; no surprises before an assessed piece.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA photographs each pupil's ordered line-up as primary evidence. Teacher frames the check as 'show me what you've got'. Nothing is eaten — allergy and choice both protected. LOOP [Feedback Policy]: Voice = order/point/say [VF, ?] → Audience: say which has most sugar; [R] once received → EVIDENCE: ordered line-up photo + check, upload same day [E: science — daily EFL; banks ELC 8939].</t>
+    <t xml:space="preserve">TA photographs each pupil's ordered line-up as primary evidence. Teacher frames the check as 'show me what you've got'. Nothing is eaten — allergy and choice both protected. LOOP [Feedback Policy]: Voice = order/point/say [VF, ?] → Audience: say which has most sugar; [R] once received → EVIDENCE: ordered line-up photo + check, upload same day [E: science — daily evidence platform; banks ELC 8939].</t>
   </si>
   <si>
     <t xml:space="preserve">Note who reads the NUMBER on the label vs who guesses from the picture.  → Influence: RAG per strand (skeleton · muscles · nutrition) sets the Aut 2 start and the ELC 8939 taster decision; weak strands become intervention lessons in Aut 2, never detentions [NS].</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  Every role from the W7 board is pre-agreed — no on-the-day negotiation; the clip can be one word + a point; weather backup agreed in advance (Pupil B: change warned early).  Pupil A: choice of task &amp; seat, own table, quiet-space option, short 10–20-min goals, opt-out of group sharing. Pupil B: colourblind-safe — labels/patterns/position, never colour alone; movement; offer choice with a reason, not commands. Pupil C: fatigue-aware — soft re-entry after rest, TA checks understanding (he may tick at random), scribe/photo instead of writing. Pupil D: middle seat, fidget/scribble pad, short 10-min bursts, answer or visibly 'park' his questions.</t>
   </si>
   <si>
-    <t xml:space="preserve">All adults work the action alongside pupils and capture evidence live.  LOOP [Feedback Policy]: Voice = do/build/record [VF] → Audience: name the impact back ('the yard IS cleaner — you did that'); [R] once received → EVIDENCE: wall + clips, same day [E: BV/community — daily EFL; banks AQA UAS].</t>
+    <t xml:space="preserve">All adults work the action alongside pupils and capture evidence live.  LOOP [Feedback Policy]: Voice = do/build/record [VF] → Audience: name the impact back ('the yard IS cleaner — you did that'); [R] once received → EVIDENCE: wall + clips, same day [E: BV/community — daily evidence platform; banks AQA UAS].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: real impact closes the BV thread — log the whole action in the SMSC tracker; note who evaluates unprompted for Grow-facing Spring targets [NS].</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  The tour is 1:1 or tiny-group by choice; playing your own clip counts as presenting; the route is walked once empty first (Pupil A, Pupil B: no surprises).  Pupil A: choice of task &amp; seat, own table, quiet-space option, short 10–20-min goals, opt-out of group sharing. Pupil B: colourblind-safe — labels/patterns/position, never colour alone; movement; offer choice with a reason, not commands. Pupil C: fatigue-aware — soft re-entry after rest, TA checks understanding (he may tick at random), scribe/photo instead of writing. Pupil D: middle seat, fidget/scribble pad, short 10-min bursts, answer or visibly 'park' his questions.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA walks each rehearsal and hosts the visitors.  LOOP [Feedback Policy]: Voice = curate/present [VF] → Audience: receive the tour fully, name one thing learned back, then [R] → EVIDENCE: clips + photos banked, same day [E: cultural — daily EFL; banks AQA UAS].</t>
+    <t xml:space="preserve">TA walks each rehearsal and hosts the visitors.  LOOP [Feedback Policy]: Voice = curate/present [VF] → Audience: receive the tour fully, name one thing learned back, then [R] → EVIDENCE: clips + photos banked, same day [E: cultural — daily evidence platform; banks AQA UAS].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: unit closed — bank the evidence set per pupil; presenting confidence feeds Spring's oracy targets and the APDR [NS].</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  The map is walked and jumped — location is physical before it's paper; stickers carry names; one continent + one ocean is the first rung, all seven the top.  Pupil A: choice of task &amp; seat, own table, quiet-space option, short 10–20-min goals, opt-out of group sharing. Pupil B: colourblind-safe — labels/patterns/position, never colour alone; movement; offer choice with a reason, not commands. Pupil C: fatigue-aware — soft re-entry after rest, TA checks understanding (he may tick at random), scribe/photo instead of writing. Pupil D: middle seat, fidget/scribble pad, short 10-min bursts, answer or visibly 'park' his questions.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA runs the atlas table and photographs each flag planting.  LOOP [Feedback Policy]: Voice = jump/label/plant + say [VF, I] → Audience: name the location back; [R] on an accurate re-do → EVIDENCE: map photos, same day [E: humanities — daily EFL; banks AQA UAS].</t>
+    <t xml:space="preserve">TA runs the atlas table and photographs each flag planting.  LOOP [Feedback Policy]: Voice = jump/label/plant + say [VF, I] → Audience: name the location back; [R] on an accurate re-do → EVIDENCE: map photos, same day [E: humanities — daily evidence platform; banks AQA UAS].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: bridges the history unit to Spring's geography — note who transfers a W4 figure to the map unprompted; RAG the unit against the W1 timeline baseline [NS].</t>
